--- a/table/Supplementary Table 6.xlsx
+++ b/table/Supplementary Table 6.xlsx
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,32 +364,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DALYs</t>
+          <t>VLW derived from DALY projections (billion constant-2023 USD)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>DALYs scenario range, low</t>
+          <t>Independently projected VLW (billion constant-2023 USD)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>DALYs scenario range, high</t>
+          <t>Absolute difference (billion constant-2023 USD)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>VLW (billion constant-2023 USD)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>VLW scenario range, low (billion constant-2023 USD)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>VLW scenario range, high (billion constant-2023 USD)</t>
+          <t>Relative difference (%)</t>
         </is>
       </c>
     </row>
@@ -404,26 +394,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D2">
-        <v>6385930.481173182</v>
+        <v>2.083540537879288</v>
       </c>
       <c r="E2">
-        <v>6256703.557875448</v>
+        <v>2.087336990145086</v>
       </c>
       <c r="F2">
-        <v>6513073.441826616</v>
+        <v>0.003796452265797612</v>
       </c>
       <c r="G2">
-        <v>753.1262011084686</v>
-      </c>
-      <c r="H2">
-        <v>737.4864135230475</v>
-      </c>
-      <c r="I2">
-        <v>768.4637947684041</v>
+        <v>0.1822115863251595</v>
       </c>
     </row>
     <row r="3">
@@ -433,30 +417,24 @@
         </is>
       </c>
       <c r="B3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D3">
-        <v>6484053.143240076</v>
+        <v>93.12106419412233</v>
       </c>
       <c r="E3">
-        <v>6229768.678892773</v>
+        <v>93.41112230699748</v>
       </c>
       <c r="F3">
-        <v>6739741.483809171</v>
+        <v>0.2900581128751583</v>
       </c>
       <c r="G3">
-        <v>759.6484931687615</v>
-      </c>
-      <c r="H3">
-        <v>728.0107627369093</v>
-      </c>
-      <c r="I3">
-        <v>791.2013331644466</v>
+        <v>0.3114849635636642</v>
       </c>
     </row>
     <row r="4">
@@ -466,30 +444,24 @@
         </is>
       </c>
       <c r="B4">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D4">
-        <v>6818412.753237404</v>
+        <v>657.9215963764671</v>
       </c>
       <c r="E4">
-        <v>6486684.596101928</v>
+        <v>650.7863042946813</v>
       </c>
       <c r="F4">
-        <v>7151017.879202027</v>
+        <v>-7.135292081785792</v>
       </c>
       <c r="G4">
-        <v>799.3056257577343</v>
-      </c>
-      <c r="H4">
-        <v>758.8036317242273</v>
-      </c>
-      <c r="I4">
-        <v>839.8809564305525</v>
+        <v>-1.084520119279218</v>
       </c>
     </row>
     <row r="5">
@@ -499,30 +471,24 @@
         </is>
       </c>
       <c r="B5">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D5">
-        <v>7145534.597800401</v>
+        <v>2.217035974448666</v>
       </c>
       <c r="E5">
-        <v>6782221.132124072</v>
+        <v>2.224628878980261</v>
       </c>
       <c r="F5">
-        <v>7512820.541764076</v>
+        <v>0.007592904531595224</v>
       </c>
       <c r="G5">
-        <v>837.9475818235107</v>
-      </c>
-      <c r="H5">
-        <v>794.9938562086805</v>
-      </c>
-      <c r="I5">
-        <v>881.2135971901121</v>
+        <v>0.3424799876548432</v>
       </c>
     </row>
     <row r="6">
@@ -532,30 +498,24 @@
         </is>
       </c>
       <c r="B6">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D6">
-        <v>7273026.55102649</v>
+        <v>97.65627697627112</v>
       </c>
       <c r="E6">
-        <v>6870876.071594755</v>
+        <v>98.2363932020214</v>
       </c>
       <c r="F6">
-        <v>7672048.94587773</v>
+        <v>0.5801162257502739</v>
       </c>
       <c r="G6">
-        <v>848.5892412711898</v>
-      </c>
-      <c r="H6">
-        <v>803.1744100930001</v>
-      </c>
-      <c r="I6">
-        <v>893.532500174393</v>
+        <v>0.5940388510727607</v>
       </c>
     </row>
     <row r="7">
@@ -565,30 +525,24 @@
         </is>
       </c>
       <c r="B7">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D7">
-        <v>7286494.066497587</v>
+        <v>659.7751802180418</v>
       </c>
       <c r="E7">
-        <v>6839017.080101709</v>
+        <v>648.9800689829819</v>
       </c>
       <c r="F7">
-        <v>7733018.368934015</v>
+        <v>-10.79511123505984</v>
       </c>
       <c r="G7">
-        <v>843.2377142402802</v>
-      </c>
-      <c r="H7">
-        <v>794.0113694502335</v>
-      </c>
-      <c r="I7">
-        <v>892.1650577323776</v>
+        <v>-1.636180256355245</v>
       </c>
     </row>
     <row r="8">
@@ -598,30 +552,24 @@
         </is>
       </c>
       <c r="B8">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D8">
-        <v>7396484.405171482</v>
+        <v>2.350531411018044</v>
       </c>
       <c r="E8">
-        <v>6882639.879354036</v>
+        <v>2.361920767815437</v>
       </c>
       <c r="F8">
-        <v>7910892.97902303</v>
+        <v>0.01138935679739328</v>
       </c>
       <c r="G8">
-        <v>851.4245789902552</v>
-      </c>
-      <c r="H8">
-        <v>795.722359303473</v>
-      </c>
-      <c r="I8">
-        <v>907.2194949305048</v>
+        <v>0.4845439096880825</v>
       </c>
     </row>
     <row r="9">
@@ -631,30 +579,24 @@
         </is>
       </c>
       <c r="B9">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D9">
-        <v>7658797.02631495</v>
+        <v>102.1914897584199</v>
       </c>
       <c r="E9">
-        <v>7076255.737006145</v>
+        <v>103.0616640970453</v>
       </c>
       <c r="F9">
-        <v>8239863.738054734</v>
+        <v>0.8701743386254037</v>
       </c>
       <c r="G9">
-        <v>880.9763258334419</v>
-      </c>
-      <c r="H9">
-        <v>818.5266408831156</v>
-      </c>
-      <c r="I9">
-        <v>943.2138483700116</v>
+        <v>0.851513507320904</v>
       </c>
     </row>
     <row r="10">
@@ -664,30 +606,24 @@
         </is>
       </c>
       <c r="B10">
-        <v>2032</v>
+        <v>2026</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D10">
-        <v>7932877.485047355</v>
+        <v>694.7636045882964</v>
       </c>
       <c r="E10">
-        <v>7310519.484959359</v>
+        <v>690.5559388182656</v>
       </c>
       <c r="F10">
-        <v>8560792.653810833</v>
+        <v>-4.207665770030758</v>
       </c>
       <c r="G10">
-        <v>912.1786418415828</v>
-      </c>
-      <c r="H10">
-        <v>847.2711250582422</v>
-      </c>
-      <c r="I10">
-        <v>977.6108227803744</v>
+        <v>-0.6056255310788969</v>
       </c>
     </row>
     <row r="11">
@@ -697,30 +633,24 @@
         </is>
       </c>
       <c r="B11">
-        <v>2033</v>
+        <v>2027</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D11">
-        <v>8088077.180221331</v>
+        <v>2.484026847587421</v>
       </c>
       <c r="E11">
-        <v>7415726.900320183</v>
+        <v>2.499212656650612</v>
       </c>
       <c r="F11">
-        <v>8753620.37696901</v>
+        <v>0.01518580906319089</v>
       </c>
       <c r="G11">
-        <v>926.7066180525624</v>
-      </c>
-      <c r="H11">
-        <v>858.8863064431592</v>
-      </c>
-      <c r="I11">
-        <v>994.0383406406784</v>
+        <v>0.6113383628659211</v>
       </c>
     </row>
     <row r="12">
@@ -730,30 +660,24 @@
         </is>
       </c>
       <c r="B12">
-        <v>2034</v>
+        <v>2027</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D12">
-        <v>8162069.659676233</v>
+        <v>106.7267025405687</v>
       </c>
       <c r="E12">
-        <v>7451352.638938699</v>
+        <v>107.8869349920692</v>
       </c>
       <c r="F12">
-        <v>8886837.656547518</v>
+        <v>1.160232451500534</v>
       </c>
       <c r="G12">
-        <v>929.8443855506274</v>
-      </c>
-      <c r="H12">
-        <v>859.2157548058652</v>
-      </c>
-      <c r="I12">
-        <v>1001.698721914306</v>
+        <v>1.087106060509561</v>
       </c>
     </row>
     <row r="13">
@@ -763,30 +687,24 @@
         </is>
       </c>
       <c r="B13">
-        <v>2035</v>
+        <v>2027</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D13">
-        <v>8285539.982833493</v>
+        <v>728.7368524353546</v>
       </c>
       <c r="E13">
-        <v>7503121.206709398</v>
+        <v>732.3760923891573</v>
       </c>
       <c r="F13">
-        <v>9062825.398312028</v>
+        <v>3.639239953802644</v>
       </c>
       <c r="G13">
-        <v>939.9219669734108</v>
-      </c>
-      <c r="H13">
-        <v>863.3420645114244</v>
-      </c>
-      <c r="I13">
-        <v>1016.125181826662</v>
+        <v>0.4993901353610323</v>
       </c>
     </row>
     <row r="14">
@@ -796,30 +714,24 @@
         </is>
       </c>
       <c r="B14">
-        <v>2036</v>
+        <v>2028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D14">
-        <v>8505909.274544235</v>
+        <v>2.617522284156799</v>
       </c>
       <c r="E14">
-        <v>7647477.319879425</v>
+        <v>2.636504545485788</v>
       </c>
       <c r="F14">
-        <v>9359705.428337911</v>
+        <v>0.01898226132898895</v>
       </c>
       <c r="G14">
-        <v>963.5906987159937</v>
-      </c>
-      <c r="H14">
-        <v>880.935063291965</v>
-      </c>
-      <c r="I14">
-        <v>1045.92975087378</v>
+        <v>0.7251996074258386</v>
       </c>
     </row>
     <row r="15">
@@ -829,30 +741,24 @@
         </is>
       </c>
       <c r="B15">
-        <v>2037</v>
+        <v>2028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D15">
-        <v>8743624.971687481</v>
+        <v>111.2619153227175</v>
       </c>
       <c r="E15">
-        <v>7841417.857998501</v>
+        <v>112.7122058870932</v>
       </c>
       <c r="F15">
-        <v>9639485.009881159</v>
+        <v>1.450290564375649</v>
       </c>
       <c r="G15">
-        <v>989.69245536339</v>
-      </c>
-      <c r="H15">
-        <v>904.133546364483</v>
-      </c>
-      <c r="I15">
-        <v>1074.243225127089</v>
+        <v>1.303492358700685</v>
       </c>
     </row>
     <row r="16">
@@ -862,30 +768,24 @@
         </is>
       </c>
       <c r="B16">
-        <v>2038</v>
+        <v>2028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D16">
-        <v>8911643.776201496</v>
+        <v>734.7098036643156</v>
       </c>
       <c r="E16">
-        <v>7950687.984453021</v>
+        <v>735.1397140030153</v>
       </c>
       <c r="F16">
-        <v>9861094.489036122</v>
+        <v>0.4299103386997558</v>
       </c>
       <c r="G16">
-        <v>1006.018453210795</v>
-      </c>
-      <c r="H16">
-        <v>916.7294846902752</v>
-      </c>
-      <c r="I16">
-        <v>1093.985807338034</v>
+        <v>0.05851430545170447</v>
       </c>
     </row>
     <row r="17">
@@ -895,30 +795,24 @@
         </is>
       </c>
       <c r="B17">
-        <v>2039</v>
+        <v>2029</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D17">
-        <v>9023413.903441371</v>
+        <v>2.751017720726177</v>
       </c>
       <c r="E17">
-        <v>8006774.564465372</v>
+        <v>2.773796434320963</v>
       </c>
       <c r="F17">
-        <v>10050503.54820297</v>
+        <v>0.02277871359478656</v>
       </c>
       <c r="G17">
-        <v>1014.454952959974</v>
-      </c>
-      <c r="H17">
-        <v>921.4897286729718</v>
-      </c>
-      <c r="I17">
-        <v>1108.159378031869</v>
+        <v>0.8280104276745168</v>
       </c>
     </row>
     <row r="18">
@@ -928,30 +822,24 @@
         </is>
       </c>
       <c r="B18">
-        <v>2040</v>
+        <v>2029</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D18">
-        <v>9158997.614921698</v>
+        <v>115.7971281048663</v>
       </c>
       <c r="E18">
-        <v>8067787.853038183</v>
+        <v>117.5374767821171</v>
       </c>
       <c r="F18">
-        <v>10248644.60090174</v>
+        <v>1.740348677250779</v>
       </c>
       <c r="G18">
-        <v>1026.231570853821</v>
-      </c>
-      <c r="H18">
-        <v>927.946720097664</v>
-      </c>
-      <c r="I18">
-        <v>1124.587783907198</v>
+        <v>1.502929049911077</v>
       </c>
     </row>
     <row r="19">
@@ -961,30 +849,24 @@
         </is>
       </c>
       <c r="B19">
-        <v>2041</v>
+        <v>2029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D19">
-        <v>9355411.454337455</v>
+        <v>724.6895684146878</v>
       </c>
       <c r="E19">
-        <v>8217538.547246261</v>
+        <v>713.9974280904653</v>
       </c>
       <c r="F19">
-        <v>10505638.22094635</v>
+        <v>-10.69214032422246</v>
       </c>
       <c r="G19">
-        <v>1046.540285890548</v>
-      </c>
-      <c r="H19">
-        <v>945.1149262674676</v>
-      </c>
-      <c r="I19">
-        <v>1148.964589017669</v>
+        <v>-1.475409718896922</v>
       </c>
     </row>
     <row r="20">
@@ -994,30 +876,24 @@
         </is>
       </c>
       <c r="B20">
-        <v>2042</v>
+        <v>2030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D20">
-        <v>9568707.450410992</v>
+        <v>2.884513157295554</v>
       </c>
       <c r="E20">
-        <v>8359553.72558366</v>
+        <v>2.911088323156138</v>
       </c>
       <c r="F20">
-        <v>10780696.23200524</v>
+        <v>0.02657516586058461</v>
       </c>
       <c r="G20">
-        <v>1069.216909815094</v>
-      </c>
-      <c r="H20">
-        <v>962.8918098161962</v>
-      </c>
-      <c r="I20">
-        <v>1176.517076838941</v>
+        <v>0.9213050664501324</v>
       </c>
     </row>
     <row r="21">
@@ -1027,30 +903,24 @@
         </is>
       </c>
       <c r="B21">
-        <v>2043</v>
+        <v>2030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D21">
-        <v>9741852.958625756</v>
+        <v>120.3323408870151</v>
       </c>
       <c r="E21">
-        <v>8471308.458223071</v>
+        <v>122.362747677141</v>
       </c>
       <c r="F21">
-        <v>11012606.38545239</v>
+        <v>2.030406790125894</v>
       </c>
       <c r="G21">
-        <v>1086.261984466742</v>
-      </c>
-      <c r="H21">
-        <v>975.3524179182706</v>
-      </c>
-      <c r="I21">
-        <v>1197.375335710911</v>
+        <v>1.687332578389982</v>
       </c>
     </row>
     <row r="22">
@@ -1060,30 +930,24 @@
         </is>
       </c>
       <c r="B22">
-        <v>2044</v>
+        <v>2030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D22">
-        <v>9876898.27660783</v>
+        <v>728.2077249459446</v>
       </c>
       <c r="E22">
-        <v>8536038.632106667</v>
+        <v>713.6534516568378</v>
       </c>
       <c r="F22">
-        <v>11218076.72703231</v>
+        <v>-14.55427328910684</v>
       </c>
       <c r="G22">
-        <v>1097.963086727399</v>
-      </c>
-      <c r="H22">
-        <v>983.1702676901144</v>
-      </c>
-      <c r="I22">
-        <v>1213.292849052719</v>
+        <v>-1.998643078139169</v>
       </c>
     </row>
     <row r="23">
@@ -1093,30 +957,24 @@
         </is>
       </c>
       <c r="B23">
-        <v>2045</v>
+        <v>2031</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D23">
-        <v>10022236.75492662</v>
+        <v>3.018008593864932</v>
       </c>
       <c r="E23">
-        <v>8613824.906902231</v>
+        <v>3.048380211991314</v>
       </c>
       <c r="F23">
-        <v>11429213.33395139</v>
+        <v>0.03037161812638223</v>
       </c>
       <c r="G23">
-        <v>1111.107918384667</v>
-      </c>
-      <c r="H23">
-        <v>991.466172193337</v>
-      </c>
-      <c r="I23">
-        <v>1230.716620629998</v>
+        <v>1.006346310216686</v>
       </c>
     </row>
     <row r="24">
@@ -1126,30 +984,24 @@
         </is>
       </c>
       <c r="B24">
-        <v>2046</v>
+        <v>2031</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D24">
-        <v>10205269.19988474</v>
+        <v>124.8675536691639</v>
       </c>
       <c r="E24">
-        <v>8738546.049833704</v>
+        <v>127.1880185721649</v>
       </c>
       <c r="F24">
-        <v>11673265.15356857</v>
+        <v>2.320464903001024</v>
       </c>
       <c r="G24">
-        <v>1129.539745088347</v>
-      </c>
-      <c r="H24">
-        <v>1006.678268296667</v>
-      </c>
-      <c r="I24">
-        <v>1252.575011173897</v>
+        <v>1.858340965939869</v>
       </c>
     </row>
     <row r="25">
@@ -1159,30 +1011,24 @@
         </is>
       </c>
       <c r="B25">
-        <v>2047</v>
+        <v>2031</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D25">
-        <v>10402453.44075263</v>
+        <v>753.0907635704132</v>
       </c>
       <c r="E25">
-        <v>8849271.664503474</v>
+        <v>747.5261588973783</v>
       </c>
       <c r="F25">
-        <v>11959275.1359653</v>
+        <v>-5.564604673034864</v>
       </c>
       <c r="G25">
-        <v>1149.956517435682</v>
-      </c>
-      <c r="H25">
-        <v>1021.554660787609</v>
-      </c>
-      <c r="I25">
-        <v>1279.774145735835</v>
+        <v>-0.7389022601542742</v>
       </c>
     </row>
     <row r="26">
@@ -1192,30 +1038,24 @@
         </is>
       </c>
       <c r="B26">
-        <v>2048</v>
+        <v>2032</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D26">
-        <v>10576977.00562762</v>
+        <v>3.15150403043431</v>
       </c>
       <c r="E26">
-        <v>8956925.689504016</v>
+        <v>3.18567210082649</v>
       </c>
       <c r="F26">
-        <v>12178493.29783582</v>
+        <v>0.03416807039217984</v>
       </c>
       <c r="G26">
-        <v>1167.194879750738</v>
-      </c>
-      <c r="H26">
-        <v>1033.707674243769</v>
-      </c>
-      <c r="I26">
-        <v>1299.321001586261</v>
+        <v>1.084182982544722</v>
       </c>
     </row>
     <row r="27">
@@ -1225,30 +1065,24 @@
         </is>
       </c>
       <c r="B27">
-        <v>2049</v>
+        <v>2032</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D27">
-        <v>10726173.77481474</v>
+        <v>129.4027664513127</v>
       </c>
       <c r="E27">
-        <v>9040484.710261021</v>
+        <v>132.0132894671888</v>
       </c>
       <c r="F27">
-        <v>12429384.81237107</v>
+        <v>2.61052301587614</v>
       </c>
       <c r="G27">
-        <v>1180.880879306403</v>
-      </c>
-      <c r="H27">
-        <v>1043.466856758762</v>
-      </c>
-      <c r="I27">
-        <v>1320.266835033303</v>
+        <v>2.01736260163985</v>
       </c>
     </row>
     <row r="28">
@@ -1258,465 +1092,381 @@
         </is>
       </c>
       <c r="B28">
-        <v>2050</v>
+        <v>2032</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D28">
-        <v>10878881.20456531</v>
+        <v>779.6243713598357</v>
       </c>
       <c r="E28">
-        <v>9103277.081217671</v>
+        <v>783.353412723168</v>
       </c>
       <c r="F28">
-        <v>12630985.45819847</v>
+        <v>3.729041363332385</v>
       </c>
       <c r="G28">
-        <v>1195.059287771596</v>
-      </c>
-      <c r="H28">
-        <v>1051.202088483295</v>
-      </c>
-      <c r="I28">
-        <v>1336.86092397161</v>
+        <v>0.4783125695298776</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B29">
-        <v>2024</v>
+        <v>2033</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D29">
-        <v>6668300.135051625</v>
+        <v>3.284999467003688</v>
       </c>
       <c r="E29">
-        <v>6489833.01982097</v>
+        <v>3.322963989661665</v>
       </c>
       <c r="F29">
-        <v>6850108.755812965</v>
+        <v>0.03796452265797789</v>
       </c>
       <c r="G29">
-        <v>792.7249088614592</v>
-      </c>
-      <c r="H29">
-        <v>769.6250146242886</v>
-      </c>
-      <c r="I29">
-        <v>816.285423557164</v>
+        <v>1.155693419110539</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B30">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D30">
-        <v>6864116.143930243</v>
+        <v>133.9379792334615</v>
       </c>
       <c r="E30">
-        <v>6585344.456203932</v>
+        <v>136.8385603622127</v>
       </c>
       <c r="F30">
-        <v>7139683.473648266</v>
+        <v>2.900581128751241</v>
       </c>
       <c r="G30">
-        <v>813.0737867585191</v>
-      </c>
-      <c r="H30">
-        <v>777.0740728031703</v>
-      </c>
-      <c r="I30">
-        <v>848.551736342708</v>
+        <v>2.165615119289924</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B31">
-        <v>2026</v>
+        <v>2033</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D31">
-        <v>7056015.823324386</v>
+        <v>789.4836393520973</v>
       </c>
       <c r="E31">
-        <v>6686728.055977402</v>
+        <v>789.4441408098339</v>
       </c>
       <c r="F31">
-        <v>7426236.894702817</v>
+        <v>-0.03949854226334537</v>
       </c>
       <c r="G31">
-        <v>833.0156859308702</v>
-      </c>
-      <c r="H31">
-        <v>785.8738229163051</v>
-      </c>
-      <c r="I31">
-        <v>880.1798715229402</v>
+        <v>-0.005003085598551542</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B32">
-        <v>2027</v>
+        <v>2034</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D32">
-        <v>7244077.500009881</v>
+        <v>3.418494903573065</v>
       </c>
       <c r="E32">
-        <v>6776068.649276694</v>
+        <v>3.460255878496841</v>
       </c>
       <c r="F32">
-        <v>7708907.334939033</v>
+        <v>0.04176097492377551</v>
       </c>
       <c r="G32">
-        <v>852.5587459763425</v>
-      </c>
-      <c r="H32">
-        <v>793.6324165423663</v>
-      </c>
-      <c r="I32">
-        <v>911.1850733368708</v>
+        <v>1.221618756258091</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B33">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D33">
-        <v>7428377.934223318</v>
+        <v>138.4731920156103</v>
       </c>
       <c r="E33">
-        <v>6866398.885259788</v>
+        <v>141.6638312572367</v>
       </c>
       <c r="F33">
-        <v>7987502.135558477</v>
+        <v>3.190639241626343</v>
       </c>
       <c r="G33">
-        <v>871.710943700342</v>
-      </c>
-      <c r="H33">
-        <v>801.692262875908</v>
-      </c>
-      <c r="I33">
-        <v>941.667161936508</v>
+        <v>2.304156635073926</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B34">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D34">
-        <v>7608992.350992906</v>
+        <v>787.952698631444</v>
       </c>
       <c r="E34">
-        <v>6945525.546176059</v>
+        <v>775.7353402182605</v>
       </c>
       <c r="F34">
-        <v>8267705.162509799</v>
+        <v>-12.21735841318355</v>
       </c>
       <c r="G34">
-        <v>890.4800963717098</v>
-      </c>
-      <c r="H34">
-        <v>808.3364797787</v>
-      </c>
-      <c r="I34">
-        <v>972.1095453166638</v>
+        <v>-1.550519267768646</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B35">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D35">
-        <v>7785994.470842712</v>
+        <v>3.551990340142442</v>
       </c>
       <c r="E35">
-        <v>7014800.990844799</v>
+        <v>3.597547767332016</v>
       </c>
       <c r="F35">
-        <v>8548881.024780871</v>
+        <v>0.04555742718957356</v>
       </c>
       <c r="G35">
-        <v>908.873864913461</v>
-      </c>
-      <c r="H35">
-        <v>814.3468136465086</v>
-      </c>
-      <c r="I35">
-        <v>1003.029415963643</v>
+        <v>1.282588713001585</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B36">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D36">
-        <v>7959456.53988282</v>
+        <v>143.0084047977592</v>
       </c>
       <c r="E36">
-        <v>7085867.972309028</v>
+        <v>146.4891021522606</v>
       </c>
       <c r="F36">
-        <v>8834959.130078422</v>
+        <v>3.480697354501416</v>
       </c>
       <c r="G36">
-        <v>926.8997570297126</v>
-      </c>
-      <c r="H36">
-        <v>820.3628358071182</v>
-      </c>
-      <c r="I36">
-        <v>1033.948739164709</v>
+        <v>2.433911041399125</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B37">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D37">
-        <v>8129449.359297682</v>
+        <v>793.3615718355092</v>
       </c>
       <c r="E37">
-        <v>7140008.103879496</v>
+        <v>776.8925437548837</v>
       </c>
       <c r="F37">
-        <v>9121801.131888898</v>
+        <v>-16.46902808062543</v>
       </c>
       <c r="G37">
-        <v>944.5651302700676</v>
-      </c>
-      <c r="H37">
-        <v>823.8182164358851</v>
-      </c>
-      <c r="I37">
-        <v>1065.021595733013</v>
+        <v>-2.07585401981633</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B38">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D38">
-        <v>8296042.314244688</v>
+        <v>3.685485776711821</v>
       </c>
       <c r="E38">
-        <v>7198366.213646475</v>
+        <v>3.734839656167192</v>
       </c>
       <c r="F38">
-        <v>9391449.731407516</v>
+        <v>0.04935387945537073</v>
       </c>
       <c r="G38">
-        <v>961.8771950327152</v>
-      </c>
-      <c r="H38">
-        <v>828.9812659238846</v>
-      </c>
-      <c r="I38">
-        <v>1093.532142915421</v>
+        <v>1.339141769783307</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B39">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D39">
-        <v>8459303.402174789</v>
+        <v>147.543617579908</v>
       </c>
       <c r="E39">
-        <v>7240080.720110877</v>
+        <v>151.3143730472845</v>
       </c>
       <c r="F39">
-        <v>9661731.062114349</v>
+        <v>3.770755467376517</v>
       </c>
       <c r="G39">
-        <v>978.8430175074679</v>
-      </c>
-      <c r="H39">
-        <v>832.3206988400149</v>
-      </c>
-      <c r="I39">
-        <v>1122.31831985919</v>
+        <v>2.55568863582616</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B40">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D40">
-        <v>8619299.260586683</v>
+        <v>812.3615953593737</v>
       </c>
       <c r="E40">
-        <v>7301367.421013604</v>
+        <v>804.9579290724358</v>
       </c>
       <c r="F40">
-        <v>9949356.700296115</v>
+        <v>-7.403666286937892</v>
       </c>
       <c r="G40">
-        <v>995.4695225599364</v>
-      </c>
-      <c r="H40">
-        <v>837.8278903133489</v>
-      </c>
-      <c r="I40">
-        <v>1154.807759323385</v>
+        <v>-0.9113757136269652</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B41">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D41">
-        <v>8776095.194225926</v>
+        <v>3.818981213281199</v>
       </c>
       <c r="E41">
-        <v>7334149.055949235</v>
+        <v>3.872131545002367</v>
       </c>
       <c r="F41">
-        <v>10215075.2545766</v>
+        <v>0.05315033172116834</v>
       </c>
       <c r="G41">
-        <v>1011.763496558022</v>
-      </c>
-      <c r="H41">
-        <v>839.9057502296904</v>
-      </c>
-      <c r="I41">
-        <v>1184.215018794574</v>
+        <v>1.391741115047344</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B42">
@@ -1724,455 +1474,3287 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D42">
-        <v>8929755.20174006</v>
+        <v>152.0788303620568</v>
       </c>
       <c r="E42">
-        <v>7351610.604085796</v>
+        <v>156.1396439423084</v>
       </c>
       <c r="F42">
-        <v>10505483.49774765</v>
+        <v>4.060813580251619</v>
       </c>
       <c r="G42">
-        <v>1027.73159014188</v>
-      </c>
-      <c r="H42">
-        <v>841.8517262330114</v>
-      </c>
-      <c r="I42">
-        <v>1214.256530297438</v>
+        <v>2.670203058889897</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B43">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D43">
-        <v>9080342.001800634</v>
+        <v>833.794643788052</v>
       </c>
       <c r="E43">
-        <v>7393393.253672212</v>
+        <v>835.9068091528288</v>
       </c>
       <c r="F43">
-        <v>10764723.23987956</v>
+        <v>2.112165364776843</v>
       </c>
       <c r="G43">
-        <v>1043.380320938479</v>
-      </c>
-      <c r="H43">
-        <v>842.7001457665018</v>
-      </c>
-      <c r="I43">
-        <v>1242.894822680191</v>
+        <v>0.2533196129901919</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B44">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D44">
-        <v>9227917.058702787</v>
+        <v>3.952476649850577</v>
       </c>
       <c r="E44">
-        <v>7410694.860755126</v>
+        <v>4.009423433837543</v>
       </c>
       <c r="F44">
-        <v>11022764.16149154</v>
+        <v>0.05694678398696595</v>
       </c>
       <c r="G44">
-        <v>1058.716076221877</v>
-      </c>
-      <c r="H44">
-        <v>843.9965165530288</v>
-      </c>
-      <c r="I44">
-        <v>1271.29267117578</v>
+        <v>1.44078736022688</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B45">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D45">
-        <v>9372540.60745283</v>
+        <v>156.6140431442056</v>
       </c>
       <c r="E45">
-        <v>7446562.754567048</v>
+        <v>160.9649148373323</v>
       </c>
       <c r="F45">
-        <v>11302504.80284047</v>
+        <v>4.35087169312672</v>
       </c>
       <c r="G45">
-        <v>1073.745115520283</v>
-      </c>
-      <c r="H45">
-        <v>846.7685682806504</v>
-      </c>
-      <c r="I45">
-        <v>1302.23496990663</v>
+        <v>2.778085289018792</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B46">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D46">
-        <v>9514271.678354086</v>
+        <v>845.4519334167385</v>
       </c>
       <c r="E46">
-        <v>7435878.785618326</v>
+        <v>844.2872456002563</v>
       </c>
       <c r="F46">
-        <v>11580352.18471957</v>
+        <v>-1.164687816482228</v>
       </c>
       <c r="G46">
-        <v>1088.473573170983</v>
-      </c>
-      <c r="H46">
-        <v>845.2599019644178</v>
-      </c>
-      <c r="I46">
-        <v>1331.111846404671</v>
+        <v>-0.1377591996005446</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B47">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D47">
-        <v>9653168.121101009</v>
+        <v>4.085972086419955</v>
       </c>
       <c r="E47">
-        <v>7465390.86425277</v>
+        <v>4.146715322672718</v>
       </c>
       <c r="F47">
-        <v>11852904.78721754</v>
+        <v>0.06074323625276357</v>
       </c>
       <c r="G47">
-        <v>1102.907460824167</v>
-      </c>
-      <c r="H47">
-        <v>846.7458922258048</v>
-      </c>
-      <c r="I47">
-        <v>1359.709558523411</v>
+        <v>1.486628762214221</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B48">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D48">
-        <v>9789286.628391411</v>
+        <v>161.1492559263544</v>
       </c>
       <c r="E48">
-        <v>7465076.759479545</v>
+        <v>165.7901857323563</v>
       </c>
       <c r="F48">
-        <v>12121458.19397255</v>
+        <v>4.640929806001822</v>
       </c>
       <c r="G48">
-        <v>1117.052669896674</v>
-      </c>
-      <c r="H48">
-        <v>844.7734136322182</v>
-      </c>
-      <c r="I48">
-        <v>1389.531160550536</v>
+        <v>2.879895274305664</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B49">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D49">
-        <v>9922682.759066457</v>
+        <v>849.2197249471996</v>
       </c>
       <c r="E49">
-        <v>7463625.920113379</v>
+        <v>836.3756145350295</v>
       </c>
       <c r="F49">
-        <v>12394665.38820609</v>
+        <v>-12.84411041217004</v>
       </c>
       <c r="G49">
-        <v>1130.914973976671</v>
-      </c>
-      <c r="H49">
-        <v>845.1289686868502</v>
-      </c>
-      <c r="I49">
-        <v>1418.852249272346</v>
+        <v>-1.512460207276583</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B50">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D50">
-        <v>10053410.96078784</v>
+        <v>4.219467522989333</v>
       </c>
       <c r="E50">
-        <v>7455791.380866018</v>
+        <v>4.284007211507894</v>
       </c>
       <c r="F50">
-        <v>12638858.49307961</v>
+        <v>0.06453968851856029</v>
       </c>
       <c r="G50">
-        <v>1144.50003118023</v>
-      </c>
-      <c r="H50">
-        <v>844.141654955273</v>
-      </c>
-      <c r="I50">
-        <v>1446.947381927933</v>
+        <v>1.529569505320812</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B51">
-        <v>2046</v>
+        <v>2040</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D51">
-        <v>10181524.59226144</v>
+        <v>165.6844687085033</v>
       </c>
       <c r="E51">
-        <v>7450354.781960918</v>
+        <v>170.6154566273802</v>
       </c>
       <c r="F51">
-        <v>12916172.35589679</v>
+        <v>4.930987918876923</v>
       </c>
       <c r="G51">
-        <v>1157.813386460774</v>
-      </c>
-      <c r="H51">
-        <v>840.0758914979032</v>
-      </c>
-      <c r="I51">
-        <v>1476.391433159321</v>
+        <v>2.976131653928438</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B52">
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Upper middle income</t>
         </is>
       </c>
       <c r="D52">
-        <v>10307075.94501649</v>
+        <v>856.3276346223289</v>
       </c>
       <c r="E52">
-        <v>7452616.194210742</v>
+        <v>838.9791861236261</v>
       </c>
       <c r="F52">
-        <v>13149532.74352802</v>
+        <v>-17.34844849870285</v>
       </c>
       <c r="G52">
-        <v>1170.860473872345</v>
-      </c>
-      <c r="H52">
-        <v>838.4745375859903</v>
-      </c>
-      <c r="I52">
-        <v>1499.596352231671</v>
+        <v>-2.02591248924883</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B53">
-        <v>2048</v>
+        <v>2041</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D53">
-        <v>10430116.26474912</v>
+        <v>4.352962959558711</v>
       </c>
       <c r="E53">
-        <v>7463955.205584987</v>
+        <v>4.421299100343069</v>
       </c>
       <c r="F53">
-        <v>13438447.74488524</v>
+        <v>0.0683361407843579</v>
       </c>
       <c r="G53">
-        <v>1183.646618787588</v>
-      </c>
-      <c r="H53">
-        <v>841.4196550170902</v>
-      </c>
-      <c r="I53">
-        <v>1532.417548668054</v>
+        <v>1.569876459304528</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B54">
-        <v>2049</v>
+        <v>2041</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>All LMICs</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="D54">
-        <v>10550695.77223915</v>
+        <v>170.2196814906521</v>
       </c>
       <c r="E54">
-        <v>7417997.595063822</v>
+        <v>175.4407275224041</v>
       </c>
       <c r="F54">
-        <v>13662934.79487643</v>
+        <v>5.221046031751996</v>
       </c>
       <c r="G54">
-        <v>1196.177040071393</v>
-      </c>
-      <c r="H54">
-        <v>833.8115370121938</v>
-      </c>
-      <c r="I54">
-        <v>1556.089970370012</v>
+        <v>3.067239925506921</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B55">
+        <v>2041</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>871.9676414403373</v>
+      </c>
+      <c r="E55">
+        <v>862.6827583776826</v>
+      </c>
+      <c r="F55">
+        <v>-9.284883062654671</v>
+      </c>
+      <c r="G55">
+        <v>-1.064819681532869</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>2042</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>4.486458396128089</v>
+      </c>
+      <c r="E56">
+        <v>4.558590989178245</v>
+      </c>
+      <c r="F56">
+        <v>0.07213259305015551</v>
+      </c>
+      <c r="G56">
+        <v>1.607784730878314</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>2042</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>174.7548942728009</v>
+      </c>
+      <c r="E57">
+        <v>180.265998417428</v>
+      </c>
+      <c r="F57">
+        <v>5.511104144627097</v>
+      </c>
+      <c r="G57">
+        <v>3.153619340711565</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>2042</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>889.9755571461649</v>
+      </c>
+      <c r="E58">
+        <v>889.6794020002915</v>
+      </c>
+      <c r="F58">
+        <v>-0.2961551458733993</v>
+      </c>
+      <c r="G58">
+        <v>-0.0332767729962229</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>2043</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>4.619953832697467</v>
+      </c>
+      <c r="E59">
+        <v>4.69588287801342</v>
+      </c>
+      <c r="F59">
+        <v>0.07592904531595313</v>
+      </c>
+      <c r="G59">
+        <v>1.643502252740482</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>2043</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>179.2901070549497</v>
+      </c>
+      <c r="E60">
+        <v>185.091269312452</v>
+      </c>
+      <c r="F60">
+        <v>5.801162257502199</v>
+      </c>
+      <c r="G60">
+        <v>3.235628754309477</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>2043</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>902.3519235790952</v>
+      </c>
+      <c r="E61">
+        <v>899.6048712863859</v>
+      </c>
+      <c r="F61">
+        <v>-2.747052292709441</v>
+      </c>
+      <c r="G61">
+        <v>-0.3044324748390309</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>2044</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>4.753449269266846</v>
+      </c>
+      <c r="E62">
+        <v>4.833174766848596</v>
+      </c>
+      <c r="F62">
+        <v>0.07972549758174985</v>
+      </c>
+      <c r="G62">
+        <v>1.677213599337443</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>2044</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>183.8253198370986</v>
+      </c>
+      <c r="E63">
+        <v>189.9165402074758</v>
+      </c>
+      <c r="F63">
+        <v>6.0912203703773</v>
+      </c>
+      <c r="G63">
+        <v>3.313591607388573</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>2044</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>909.3843176210332</v>
+      </c>
+      <c r="E64">
+        <v>896.2018584490883</v>
+      </c>
+      <c r="F64">
+        <v>-13.18245917194486</v>
+      </c>
+      <c r="G64">
+        <v>-1.449602650552675</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>2045</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>4.886944705836224</v>
+      </c>
+      <c r="E65">
+        <v>4.970466655683771</v>
+      </c>
+      <c r="F65">
+        <v>0.08352194984754746</v>
+      </c>
+      <c r="G65">
+        <v>1.709083177221169</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>2045</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>188.3605326192474</v>
+      </c>
+      <c r="E66">
+        <v>194.7418111024998</v>
+      </c>
+      <c r="F66">
+        <v>6.381278483252402</v>
+      </c>
+      <c r="G66">
+        <v>3.387800190686198</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>2045</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>917.8604410595836</v>
+      </c>
+      <c r="E67">
+        <v>900.1433466397336</v>
+      </c>
+      <c r="F67">
+        <v>-17.71709441985001</v>
+      </c>
+      <c r="G67">
+        <v>-1.930260160182663</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>2046</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>5.020440142405602</v>
+      </c>
+      <c r="E68">
+        <v>5.107758544518947</v>
+      </c>
+      <c r="F68">
+        <v>0.08731840211334507</v>
+      </c>
+      <c r="G68">
+        <v>1.739257906409486</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>2046</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>192.8957454013962</v>
+      </c>
+      <c r="E69">
+        <v>199.5670819975237</v>
+      </c>
+      <c r="F69">
+        <v>6.671336596127503</v>
+      </c>
+      <c r="G69">
+        <v>3.458519306501622</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>2046</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>931.6235595445452</v>
+      </c>
+      <c r="E70">
+        <v>920.5838090388766</v>
+      </c>
+      <c r="F70">
+        <v>-11.03975050566874</v>
+      </c>
+      <c r="G70">
+        <v>-1.185001215626822</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>2047</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>5.15393557897498</v>
+      </c>
+      <c r="E71">
+        <v>5.245050433354122</v>
+      </c>
+      <c r="F71">
+        <v>0.09111485437914268</v>
+      </c>
+      <c r="G71">
+        <v>1.767869485036592</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>2047</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>197.430958183545</v>
+      </c>
+      <c r="E72">
+        <v>204.3923528925476</v>
+      </c>
+      <c r="F72">
+        <v>6.961394709002576</v>
+      </c>
+      <c r="G72">
+        <v>3.525989425898849</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>2047</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>947.3716236731618</v>
+      </c>
+      <c r="E73">
+        <v>944.39251367699</v>
+      </c>
+      <c r="F73">
+        <v>-2.979109996171815</v>
+      </c>
+      <c r="G73">
+        <v>-0.3144605476593409</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>2048</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>5.287431015544358</v>
+      </c>
+      <c r="E74">
+        <v>5.382342322189298</v>
+      </c>
+      <c r="F74">
+        <v>0.0949113066449403</v>
+      </c>
+      <c r="G74">
+        <v>1.795036310940293</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>2048</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>201.9661709656938</v>
+      </c>
+      <c r="E75">
+        <v>209.2176237875716</v>
+      </c>
+      <c r="F75">
+        <v>7.251452821877677</v>
+      </c>
+      <c r="G75">
+        <v>3.590429420533707</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>2048</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>959.9412777694996</v>
+      </c>
+      <c r="E76">
+        <v>955.3336057570118</v>
+      </c>
+      <c r="F76">
+        <v>-4.607672012487683</v>
+      </c>
+      <c r="G76">
+        <v>-0.4799951954554947</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>2049</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>5.420926452113736</v>
+      </c>
+      <c r="E77">
+        <v>5.519634211024473</v>
+      </c>
+      <c r="F77">
+        <v>0.09870775891073702</v>
+      </c>
+      <c r="G77">
+        <v>1.820865119323815</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>2049</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>206.5013837478427</v>
+      </c>
+      <c r="E78">
+        <v>214.0428946825954</v>
+      </c>
+      <c r="F78">
+        <v>7.541510934752779</v>
+      </c>
+      <c r="G78">
+        <v>3.652038934500149</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>2049</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D79">
+        <v>968.9585691064468</v>
+      </c>
+      <c r="E79">
+        <v>955.427459440779</v>
+      </c>
+      <c r="F79">
+        <v>-13.53110966566794</v>
+      </c>
+      <c r="G79">
+        <v>-1.396459053780395</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B80">
         <v>2050</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>All LMICs</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>10668863.68384837</v>
-      </c>
-      <c r="E55">
-        <v>7395645.411140123</v>
-      </c>
-      <c r="F55">
-        <v>13932763.26519256</v>
-      </c>
-      <c r="G55">
-        <v>1208.45685221105</v>
-      </c>
-      <c r="H55">
-        <v>830.7994720229001</v>
-      </c>
-      <c r="I55">
-        <v>1586.555391080247</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>5.554421888683114</v>
+      </c>
+      <c r="E80">
+        <v>5.656926099859649</v>
+      </c>
+      <c r="F80">
+        <v>0.1025042111765346</v>
+      </c>
+      <c r="G80">
+        <v>1.84545238425951</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>2050</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>211.0365965299915</v>
+      </c>
+      <c r="E81">
+        <v>218.8681655776194</v>
+      </c>
+      <c r="F81">
+        <v>7.83156904762788</v>
+      </c>
+      <c r="G81">
+        <v>3.711000450348381</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>2050</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>978.4682693529218</v>
+      </c>
+      <c r="E82">
+        <v>960.5717362997044</v>
+      </c>
+      <c r="F82">
+        <v>-17.89653305321747</v>
+      </c>
+      <c r="G82">
+        <v>-1.829035607363411</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>2024</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>2.080968273743164</v>
+      </c>
+      <c r="E83">
+        <v>2.085330273584192</v>
+      </c>
+      <c r="F83">
+        <v>0.00436199984102803</v>
+      </c>
+      <c r="G83">
+        <v>0.2096139521234428</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>2024</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>93.144189723254</v>
+      </c>
+      <c r="E84">
+        <v>93.24057115957596</v>
+      </c>
+      <c r="F84">
+        <v>0.0963814363219484</v>
+      </c>
+      <c r="G84">
+        <v>0.1034755217779153</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>2024</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D85">
+        <v>697.499750864462</v>
+      </c>
+      <c r="E85">
+        <v>696.6780652324724</v>
+      </c>
+      <c r="F85">
+        <v>-0.8216856319896806</v>
+      </c>
+      <c r="G85">
+        <v>-0.1178044337609162</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>2025</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>2.209234203420767</v>
+      </c>
+      <c r="E86">
+        <v>2.217353193589952</v>
+      </c>
+      <c r="F86">
+        <v>0.008118990169184936</v>
+      </c>
+      <c r="G86">
+        <v>0.3675024656332739</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>2025</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>97.62234331201228</v>
+      </c>
+      <c r="E87">
+        <v>97.88141150896716</v>
+      </c>
+      <c r="F87">
+        <v>0.2590681969548712</v>
+      </c>
+      <c r="G87">
+        <v>0.2653779741046159</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>2025</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>713.242209243086</v>
+      </c>
+      <c r="E88">
+        <v>711.6151512058988</v>
+      </c>
+      <c r="F88">
+        <v>-1.627058037187226</v>
+      </c>
+      <c r="G88">
+        <v>-0.2281213893543833</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>2026</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>2.334934809056727</v>
+      </c>
+      <c r="E89">
+        <v>2.346192849408023</v>
+      </c>
+      <c r="F89">
+        <v>0.01125804035129585</v>
+      </c>
+      <c r="G89">
+        <v>0.4821565170739779</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>2026</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>102.0109337624266</v>
+      </c>
+      <c r="E90">
+        <v>102.4294349964236</v>
+      </c>
+      <c r="F90">
+        <v>0.4185012339970058</v>
+      </c>
+      <c r="G90">
+        <v>0.4102513510675767</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>2026</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>728.6698173593869</v>
+      </c>
+      <c r="E91">
+        <v>726.2534528182174</v>
+      </c>
+      <c r="F91">
+        <v>-2.416364541169514</v>
+      </c>
+      <c r="G91">
+        <v>-0.3316130960283401</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>2027</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>2.45812139724084</v>
+      </c>
+      <c r="E92">
+        <v>2.471925994157395</v>
+      </c>
+      <c r="F92">
+        <v>0.01380459691655567</v>
+      </c>
+      <c r="G92">
+        <v>0.5615913409342139</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>2027</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>106.3117523385952</v>
+      </c>
+      <c r="E93">
+        <v>106.8864979602829</v>
+      </c>
+      <c r="F93">
+        <v>0.5747456216877396</v>
+      </c>
+      <c r="G93">
+        <v>0.5406228465289675</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>2027</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>743.7888722405064</v>
+      </c>
+      <c r="E94">
+        <v>740.5989466096049</v>
+      </c>
+      <c r="F94">
+        <v>-3.189925630901485</v>
+      </c>
+      <c r="G94">
+        <v>-0.4288751485744213</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>2028</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>2.578844248428924</v>
+      </c>
+      <c r="E95">
+        <v>2.59462753032798</v>
+      </c>
+      <c r="F95">
+        <v>0.01578328189905553</v>
+      </c>
+      <c r="G95">
+        <v>0.6120292805069938</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>2028</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>110.5265544793078</v>
+      </c>
+      <c r="E96">
+        <v>111.2544196120941</v>
+      </c>
+      <c r="F96">
+        <v>0.7278651327862917</v>
+      </c>
+      <c r="G96">
+        <v>0.6585432217762284</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>2028</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>758.6055449726053</v>
+      </c>
+      <c r="E97">
+        <v>754.657489572373</v>
+      </c>
+      <c r="F97">
+        <v>-3.948055400232306</v>
+      </c>
+      <c r="G97">
+        <v>-0.5204358742691338</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>2029</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>2.697152637465547</v>
+      </c>
+      <c r="E98">
+        <v>2.714370554401958</v>
+      </c>
+      <c r="F98">
+        <v>0.01721791693641084</v>
+      </c>
+      <c r="G98">
+        <v>0.6383738427421787</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>2029</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>114.6570605145521</v>
+      </c>
+      <c r="E99">
+        <v>115.5349827791534</v>
+      </c>
+      <c r="F99">
+        <v>0.8779222646013096</v>
+      </c>
+      <c r="G99">
+        <v>0.7656940276171526</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>2029</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>773.1258832196921</v>
+      </c>
+      <c r="E100">
+        <v>768.4348215422668</v>
+      </c>
+      <c r="F100">
+        <v>-4.691061677425296</v>
+      </c>
+      <c r="G100">
+        <v>-0.606765570684209</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>2030</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>2.813094853696294</v>
+      </c>
+      <c r="E101">
+        <v>2.831226400399255</v>
+      </c>
+      <c r="F101">
+        <v>0.01813154670296147</v>
+      </c>
+      <c r="G101">
+        <v>0.6445408934269437</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>2030</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>118.7049563676906</v>
+      </c>
+      <c r="E102">
+        <v>119.7299346321902</v>
+      </c>
+      <c r="F102">
+        <v>1.024978264499666</v>
+      </c>
+      <c r="G102">
+        <v>0.8634671170130239</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>2030</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D103">
+        <v>787.3558136920742</v>
+      </c>
+      <c r="E103">
+        <v>781.9365675419307</v>
+      </c>
+      <c r="F103">
+        <v>-5.419246150143522</v>
+      </c>
+      <c r="G103">
+        <v>-0.688284261816974</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>2031</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D104">
+        <v>2.926718220677784</v>
+      </c>
+      <c r="E104">
+        <v>2.945264682373054</v>
+      </c>
+      <c r="F104">
+        <v>0.01854646169527064</v>
+      </c>
+      <c r="G104">
+        <v>0.6336948177735933</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>2031</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D105">
+        <v>122.6718942435934</v>
+      </c>
+      <c r="E105">
+        <v>123.8409873984986</v>
+      </c>
+      <c r="F105">
+        <v>1.169093154905298</v>
+      </c>
+      <c r="G105">
+        <v>0.9530244577325866</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>2031</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D106">
+        <v>801.3011445654415</v>
+      </c>
+      <c r="E106">
+        <v>795.1682400774982</v>
+      </c>
+      <c r="F106">
+        <v>-6.132904487943279</v>
+      </c>
+      <c r="G106">
+        <v>-0.7653682425811648</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>2032</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D107">
+        <v>3.038069115493496</v>
+      </c>
+      <c r="E107">
+        <v>3.0565533358807</v>
+      </c>
+      <c r="F107">
+        <v>0.01848422038720399</v>
+      </c>
+      <c r="G107">
+        <v>0.608420009042535</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>2032</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D108">
+        <v>126.5594933030086</v>
+      </c>
+      <c r="E108">
+        <v>127.8698190608066</v>
+      </c>
+      <c r="F108">
+        <v>1.310325757797969</v>
+      </c>
+      <c r="G108">
+        <v>1.035343713537781</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>2032</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D109">
+        <v>814.9675678515654</v>
+      </c>
+      <c r="E109">
+        <v>808.1352413892434</v>
+      </c>
+      <c r="F109">
+        <v>-6.83232646232193</v>
+      </c>
+      <c r="G109">
+        <v>-0.8383556268789263</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>2033</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D110">
+        <v>3.147192987683267</v>
+      </c>
+      <c r="E110">
+        <v>3.165158658454658</v>
+      </c>
+      <c r="F110">
+        <v>0.01796567077139111</v>
+      </c>
+      <c r="G110">
+        <v>0.5708474453807206</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>2033</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D111">
+        <v>130.3693403234456</v>
+      </c>
+      <c r="E111">
+        <v>131.8180740421676</v>
+      </c>
+      <c r="F111">
+        <v>1.448733718722053</v>
+      </c>
+      <c r="G111">
+        <v>1.111253393725667</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>2033</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D112">
+        <v>828.3606617215864</v>
+      </c>
+      <c r="E112">
+        <v>820.8428656572128</v>
+      </c>
+      <c r="F112">
+        <v>-7.51779606437367</v>
+      </c>
+      <c r="G112">
+        <v>-0.9075510718663768</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>2034</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D113">
+        <v>3.254134377794211</v>
+      </c>
+      <c r="E113">
+        <v>3.271145349097685</v>
+      </c>
+      <c r="F113">
+        <v>0.01701097130347362</v>
+      </c>
+      <c r="G113">
+        <v>0.5227495035101891</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>2034</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D114">
+        <v>134.1029903468395</v>
+      </c>
+      <c r="E114">
+        <v>135.6873638771546</v>
+      </c>
+      <c r="F114">
+        <v>1.584373530315105</v>
+      </c>
+      <c r="G114">
+        <v>1.181460253956556</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>2034</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D115">
+        <v>841.4858927828343</v>
+      </c>
+      <c r="E115">
+        <v>833.2963011627382</v>
+      </c>
+      <c r="F115">
+        <v>-8.189591620096053</v>
+      </c>
+      <c r="G115">
+        <v>-0.9732298176755738</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>2035</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D116">
+        <v>3.358936935560605</v>
+      </c>
+      <c r="E116">
+        <v>3.374576546825686</v>
+      </c>
+      <c r="F116">
+        <v>0.0156396112650814</v>
+      </c>
+      <c r="G116">
+        <v>0.4656119351187269</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>2035</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D117">
+        <v>137.761967314264</v>
+      </c>
+      <c r="E117">
+        <v>139.47926786963</v>
+      </c>
+      <c r="F117">
+        <v>1.717300555365995</v>
+      </c>
+      <c r="G117">
+        <v>1.246570870644197</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>2035</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D118">
+        <v>854.3486183101119</v>
+      </c>
+      <c r="E118">
+        <v>845.500632406714</v>
+      </c>
+      <c r="F118">
+        <v>-8.847985903397898</v>
+      </c>
+      <c r="G118">
+        <v>-1.03564115558577</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>2036</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D119">
+        <v>3.461643437720185</v>
+      </c>
+      <c r="E119">
+        <v>3.475513868281273</v>
+      </c>
+      <c r="F119">
+        <v>0.0138704305610875</v>
+      </c>
+      <c r="G119">
+        <v>0.400689175839048</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>2036</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>141.3477646879484</v>
+      </c>
+      <c r="E120">
+        <v>143.1953337373602</v>
+      </c>
+      <c r="F120">
+        <v>1.84756904941176</v>
+      </c>
+      <c r="G120">
+        <v>1.307108784840435</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>2036</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D121">
+        <v>866.9540884323537</v>
+      </c>
+      <c r="E121">
+        <v>857.4608421855013</v>
+      </c>
+      <c r="F121">
+        <v>-9.493246246852436</v>
+      </c>
+      <c r="G121">
+        <v>-1.095011416811972</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>2037</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D122">
+        <v>3.56229580547412</v>
+      </c>
+      <c r="E122">
+        <v>3.574017444440386</v>
+      </c>
+      <c r="F122">
+        <v>0.01172163896626666</v>
+      </c>
+      <c r="G122">
+        <v>0.3290473224669948</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>2037</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D123">
+        <v>144.8618460608554</v>
+      </c>
+      <c r="E123">
+        <v>146.8370782437381</v>
+      </c>
+      <c r="F123">
+        <v>1.97523218288265</v>
+      </c>
+      <c r="G123">
+        <v>1.363528241972609</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>2037</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D124">
+        <v>879.3074482755504</v>
+      </c>
+      <c r="E124">
+        <v>869.1818136253096</v>
+      </c>
+      <c r="F124">
+        <v>-10.12563465024084</v>
+      </c>
+      <c r="G124">
+        <v>-1.151546557475281</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>2038</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D125">
+        <v>3.660935121597769</v>
+      </c>
+      <c r="E125">
+        <v>3.670145956433876</v>
+      </c>
+      <c r="F125">
+        <v>0.009210834836107296</v>
+      </c>
+      <c r="G125">
+        <v>0.2515978713134731</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>2038</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D126">
+        <v>148.3056457540667</v>
+      </c>
+      <c r="E126">
+        <v>150.4059878168706</v>
+      </c>
+      <c r="F126">
+        <v>2.100342062803946</v>
+      </c>
+      <c r="G126">
+        <v>1.416225290766689</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>2038</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D127">
+        <v>891.4137400628148</v>
+      </c>
+      <c r="E127">
+        <v>880.668332175884</v>
+      </c>
+      <c r="F127">
+        <v>-10.74540788693082</v>
+      </c>
+      <c r="G127">
+        <v>-1.205434402006596</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>2039</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D128">
+        <v>3.757601647209244</v>
+      </c>
+      <c r="E128">
+        <v>3.763956670505375</v>
+      </c>
+      <c r="F128">
+        <v>0.006355023296130913</v>
+      </c>
+      <c r="G128">
+        <v>0.1691244547130419</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>2039</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D129">
+        <v>151.6805694022208</v>
+      </c>
+      <c r="E129">
+        <v>153.9035191562852</v>
+      </c>
+      <c r="F129">
+        <v>2.222949754064359</v>
+      </c>
+      <c r="G129">
+        <v>1.465546815142568</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>2039</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D130">
+        <v>903.2779051724472</v>
+      </c>
+      <c r="E130">
+        <v>891.9250875643135</v>
+      </c>
+      <c r="F130">
+        <v>-11.3528176081337</v>
+      </c>
+      <c r="G130">
+        <v>-1.25684659650413</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>2040</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D131">
+        <v>3.852334838202582</v>
+      </c>
+      <c r="E131">
+        <v>3.855505472126275</v>
+      </c>
+      <c r="F131">
+        <v>0.003170633923692989</v>
+      </c>
+      <c r="G131">
+        <v>0.08230421437541344</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>2040</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D132">
+        <v>154.9879945272428</v>
+      </c>
+      <c r="E132">
+        <v>157.3310998275011</v>
+      </c>
+      <c r="F132">
+        <v>2.343105300258259</v>
+      </c>
+      <c r="G132">
+        <v>1.511797934675774</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>2040</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D133">
+        <v>914.9047861548376</v>
+      </c>
+      <c r="E133">
+        <v>902.9566757097572</v>
+      </c>
+      <c r="F133">
+        <v>-11.9481104450806</v>
+      </c>
+      <c r="G133">
+        <v>-1.305940314871029</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>2041</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D134">
+        <v>3.945173361352265</v>
+      </c>
+      <c r="E134">
+        <v>3.944846899288158</v>
+      </c>
+      <c r="F134">
+        <v>-0.0003264620641068028</v>
+      </c>
+      <c r="G134">
+        <v>-0.008274973852984327</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>2041</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D135">
+        <v>158.2292711005988</v>
+      </c>
+      <c r="E135">
+        <v>160.6901288447106</v>
+      </c>
+      <c r="F135">
+        <v>2.46085774411182</v>
+      </c>
+      <c r="G135">
+        <v>1.555248107379107</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>2041</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D136">
+        <v>926.2991287090324</v>
+      </c>
+      <c r="E136">
+        <v>913.7676005998708</v>
+      </c>
+      <c r="F136">
+        <v>-12.53152810916174</v>
+      </c>
+      <c r="G136">
+        <v>-1.352859753482304</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>2042</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D137">
+        <v>4.036155110095641</v>
+      </c>
+      <c r="E137">
+        <v>4.032034174992484</v>
+      </c>
+      <c r="F137">
+        <v>-0.004120935103157031</v>
+      </c>
+      <c r="G137">
+        <v>-0.102100513750062</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>2042</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D138">
+        <v>161.4057220943053</v>
+      </c>
+      <c r="E138">
+        <v>163.9819772418055</v>
+      </c>
+      <c r="F138">
+        <v>2.576255147500234</v>
+      </c>
+      <c r="G138">
+        <v>1.596136192739804</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>2042</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D139">
+        <v>937.465583619766</v>
+      </c>
+      <c r="E139">
+        <v>924.3622761296994</v>
+      </c>
+      <c r="F139">
+        <v>-13.10330749006675</v>
+      </c>
+      <c r="G139">
+        <v>-1.397737444341362</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>2043</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D140">
+        <v>4.125317219999704</v>
+      </c>
+      <c r="E140">
+        <v>4.117119238956912</v>
+      </c>
+      <c r="F140">
+        <v>-0.008197981042791902</v>
+      </c>
+      <c r="G140">
+        <v>-0.1987236521605601</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>2043</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D141">
+        <v>164.518644020919</v>
+      </c>
+      <c r="E141">
+        <v>167.2079886319835</v>
+      </c>
+      <c r="F141">
+        <v>2.689344611064485</v>
+      </c>
+      <c r="G141">
+        <v>1.634674675973215</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>2043</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D142">
+        <v>948.4087086557556</v>
+      </c>
+      <c r="E142">
+        <v>934.7450279037864</v>
+      </c>
+      <c r="F142">
+        <v>-13.66368075196942</v>
+      </c>
+      <c r="G142">
+        <v>-1.440695411932255</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>2044</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D143">
+        <v>4.212696083918526</v>
+      </c>
+      <c r="E143">
+        <v>4.200152778557135</v>
+      </c>
+      <c r="F143">
+        <v>-0.01254330536139037</v>
+      </c>
+      <c r="G143">
+        <v>-0.2977500657897674</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>2044</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D144">
+        <v>167.5693074627261</v>
+      </c>
+      <c r="E144">
+        <v>170.3694797561623</v>
+      </c>
+      <c r="F144">
+        <v>2.800172293436276</v>
+      </c>
+      <c r="G144">
+        <v>1.671053211256568</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>2044</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D145">
+        <v>959.1329704300268</v>
+      </c>
+      <c r="E145">
+        <v>944.9200950022358</v>
+      </c>
+      <c r="F145">
+        <v>-14.212875427791</v>
+      </c>
+      <c r="G145">
+        <v>-1.481846195050376</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>2045</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D146">
+        <v>4.298327366847559</v>
+      </c>
+      <c r="E146">
+        <v>4.281184259022665</v>
+      </c>
+      <c r="F146">
+        <v>-0.01714310782489381</v>
+      </c>
+      <c r="G146">
+        <v>-0.3988320656336317</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>2045</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D147">
+        <v>170.5589575903482</v>
+      </c>
+      <c r="E147">
+        <v>173.467741020426</v>
+      </c>
+      <c r="F147">
+        <v>2.908783430077761</v>
+      </c>
+      <c r="G147">
+        <v>1.705441608680638</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>2045</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D148">
+        <v>969.6427462230338</v>
+      </c>
+      <c r="E148">
+        <v>954.8916317114482</v>
+      </c>
+      <c r="F148">
+        <v>-14.75111451158557</v>
+      </c>
+      <c r="G148">
+        <v>-1.521293751646606</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>2046</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D149">
+        <v>4.382246020480824</v>
+      </c>
+      <c r="E149">
+        <v>4.360261952904548</v>
+      </c>
+      <c r="F149">
+        <v>-0.0219840675762768</v>
+      </c>
+      <c r="G149">
+        <v>-0.5016621037142202</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>2046</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D150">
+        <v>173.4888146709761</v>
+      </c>
+      <c r="E150">
+        <v>176.5040370227214</v>
+      </c>
+      <c r="F150">
+        <v>3.015222351745308</v>
+      </c>
+      <c r="G150">
+        <v>1.737992364213058</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>2046</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D151">
+        <v>979.9423257693174</v>
+      </c>
+      <c r="E151">
+        <v>964.6637092202368</v>
+      </c>
+      <c r="F151">
+        <v>-15.27861654908077</v>
+      </c>
+      <c r="G151">
+        <v>-1.55913426201752</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>2047</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D152">
+        <v>4.464486297476984</v>
+      </c>
+      <c r="E152">
+        <v>4.437432968832571</v>
+      </c>
+      <c r="F152">
+        <v>-0.02705332864441257</v>
+      </c>
+      <c r="G152">
+        <v>-0.6059673351377789</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>2047</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D153">
+        <v>176.3600745664384</v>
+      </c>
+      <c r="E153">
+        <v>179.4796070690215</v>
+      </c>
+      <c r="F153">
+        <v>3.119532502583155</v>
+      </c>
+      <c r="G153">
+        <v>1.768842812213693</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>2047</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D154">
+        <v>990.0359130084296</v>
+      </c>
+      <c r="E154">
+        <v>974.2403172820156</v>
+      </c>
+      <c r="F154">
+        <v>-15.79559572641392</v>
+      </c>
+      <c r="G154">
+        <v>-1.595456843420531</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>2048</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D155">
+        <v>4.545081765440066</v>
+      </c>
+      <c r="E155">
+        <v>4.512743279579095</v>
+      </c>
+      <c r="F155">
+        <v>-0.03233848586097121</v>
+      </c>
+      <c r="G155">
+        <v>-0.7115050406104217</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>2048</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D156">
+        <v>179.1739092213095</v>
+      </c>
+      <c r="E156">
+        <v>182.3956656791653</v>
+      </c>
+      <c r="F156">
+        <v>3.221756457855861</v>
+      </c>
+      <c r="G156">
+        <v>1.798116964605855</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>2048</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D157">
+        <v>999.9276278008384</v>
+      </c>
+      <c r="E157">
+        <v>983.6253658437416</v>
+      </c>
+      <c r="F157">
+        <v>-16.30226195709702</v>
+      </c>
+      <c r="G157">
+        <v>-1.630344187303927</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>2049</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D158">
+        <v>4.624065320620598</v>
+      </c>
+      <c r="E158">
+        <v>4.586237749446227</v>
+      </c>
+      <c r="F158">
+        <v>-0.03782757117437097</v>
+      </c>
+      <c r="G158">
+        <v>-0.8180587546132265</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>2049</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D159">
+        <v>181.9314671412548</v>
+      </c>
+      <c r="E159">
+        <v>185.2534030825805</v>
+      </c>
+      <c r="F159">
+        <v>3.321935941325705</v>
+      </c>
+      <c r="G159">
+        <v>1.825927088658332</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>2049</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D160">
+        <v>1009.621507609517</v>
+      </c>
+      <c r="E160">
+        <v>992.82268664227</v>
+      </c>
+      <c r="F160">
+        <v>-16.79882096724714</v>
+      </c>
+      <c r="G160">
+        <v>-1.663873128755125</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>2050</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="D161">
+        <v>4.701469201342696</v>
+      </c>
+      <c r="E161">
+        <v>4.657960160992646</v>
+      </c>
+      <c r="F161">
+        <v>-0.04350904035004977</v>
+      </c>
+      <c r="G161">
+        <v>-0.925434975467328</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>2050</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="D162">
+        <v>184.6338738618096</v>
+      </c>
+      <c r="E162">
+        <v>188.0539857040922</v>
+      </c>
+      <c r="F162">
+        <v>3.420111842282637</v>
+      </c>
+      <c r="G162">
+        <v>1.852375065716512</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>2050</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="D163">
+        <v>1019.121509147897</v>
+      </c>
+      <c r="E163">
+        <v>1001.836034768781</v>
+      </c>
+      <c r="F163">
+        <v>-17.28547437911664</v>
+      </c>
+      <c r="G163">
+        <v>-1.696115156432061</v>
       </c>
     </row>
   </sheetData>
